--- a/data/employees/EMP074/AST-EMP074-06.xlsx
+++ b/data/employees/EMP074/AST-EMP074-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,215 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Skills Matrix - Morgan Smith (HR)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Morgan Smith | Role: Manager | Location: Hsinchu | Date: 2025-03-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>86</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>61</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Skills</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Last Review Date</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Rating</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>77</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP074</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp074 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure AI, Fabric</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>64</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4.2</v>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP074</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp074 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Synapse, TypeScript</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>91</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3.9</v>
+          <t>Section 1: Department KPI performance. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EMP016</t>
+          <t>EMP074</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Avery Wilson</t>
+          <t>Ast Emp074 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Python, SQL</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMP021</t>
+          <t>EMP074</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alex Garcia</t>
+          <t>Ast Emp074 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>99</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>84</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>63</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>67</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>93</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>98</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>62</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>97</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp074 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>64</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ontology, MLOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP074</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP074 contributes to ast emp074 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>